--- a/website_content_creation/authors/Mallory_West/MWest_Author_form.xlsx
+++ b/website_content_creation/authors/Mallory_West/MWest_Author_form.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\esmender\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://041gc-my.sharepoint.com/personal/emily_smenderovac_nrcan-rncan_gc_ca/Documents/Documents/WET lab/GLFC-WET.github.io/website_content_creation/authors/Mallory_West/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8ADC2EDB-7ED2-4397-AACC-E0C46A958D74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{8ADC2EDB-7ED2-4397-AACC-E0C46A958D74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E87FE44D-C83C-4F15-942A-775A4ED3BA21}"/>
   <bookViews>
-    <workbookView xWindow="17010" yWindow="-12615" windowWidth="21600" windowHeight="11235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-14235" yWindow="-16395" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -150,7 +150,7 @@
     <t>Mallory West</t>
   </si>
   <si>
-    <t>Visiting and Co-supervised Students</t>
+    <t>Past WETlab Members</t>
   </si>
 </sst>
 </file>
